--- a/TOR330 Data/5. Clean Data for Data Visualisation/TOR330_finisher_anomalies.xlsx
+++ b/TOR330 Data/5. Clean Data for Data Visualisation/TOR330_finisher_anomalies.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="88">
   <si>
     <t>Name</t>
   </si>
@@ -639,7 +639,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BF41"/>
+  <dimension ref="A1:BF57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:58">
@@ -3418,8 +3418,8 @@
       <c r="A34" t="s">
         <v>58</v>
       </c>
-      <c r="B34" t="s">
-        <v>66</v>
+      <c r="B34">
+        <v>48</v>
       </c>
       <c r="C34" t="s">
         <v>74</v>
@@ -3427,8 +3427,8 @@
       <c r="D34" t="s">
         <v>76</v>
       </c>
-      <c r="E34" t="s">
-        <v>83</v>
+      <c r="E34">
+        <v>2023</v>
       </c>
       <c r="F34" t="s">
         <v>84</v>
@@ -3498,8 +3498,8 @@
       <c r="A35" t="s">
         <v>59</v>
       </c>
-      <c r="B35" t="s">
-        <v>67</v>
+      <c r="B35">
+        <v>275</v>
       </c>
       <c r="C35" t="s">
         <v>74</v>
@@ -3507,8 +3507,8 @@
       <c r="D35" t="s">
         <v>77</v>
       </c>
-      <c r="E35" t="s">
-        <v>83</v>
+      <c r="E35">
+        <v>2023</v>
       </c>
       <c r="F35" t="s">
         <v>84</v>
@@ -3605,8 +3605,8 @@
       <c r="A36" t="s">
         <v>60</v>
       </c>
-      <c r="B36" t="s">
-        <v>68</v>
+      <c r="B36">
+        <v>493</v>
       </c>
       <c r="C36" t="s">
         <v>75</v>
@@ -3614,8 +3614,8 @@
       <c r="D36" t="s">
         <v>78</v>
       </c>
-      <c r="E36" t="s">
-        <v>83</v>
+      <c r="E36">
+        <v>2023</v>
       </c>
       <c r="F36" t="s">
         <v>84</v>
@@ -3703,8 +3703,8 @@
       <c r="A37" t="s">
         <v>61</v>
       </c>
-      <c r="B37" t="s">
-        <v>69</v>
+      <c r="B37">
+        <v>540</v>
       </c>
       <c r="C37" t="s">
         <v>75</v>
@@ -3712,8 +3712,8 @@
       <c r="D37" t="s">
         <v>77</v>
       </c>
-      <c r="E37" t="s">
-        <v>83</v>
+      <c r="E37">
+        <v>2023</v>
       </c>
       <c r="F37" t="s">
         <v>84</v>
@@ -3753,8 +3753,8 @@
       <c r="A38" t="s">
         <v>62</v>
       </c>
-      <c r="B38" t="s">
-        <v>70</v>
+      <c r="B38">
+        <v>665</v>
       </c>
       <c r="C38" t="s">
         <v>74</v>
@@ -3762,8 +3762,8 @@
       <c r="D38" t="s">
         <v>79</v>
       </c>
-      <c r="E38" t="s">
-        <v>83</v>
+      <c r="E38">
+        <v>2023</v>
       </c>
       <c r="F38" t="s">
         <v>84</v>
@@ -3830,8 +3830,8 @@
       <c r="A39" t="s">
         <v>63</v>
       </c>
-      <c r="B39" t="s">
-        <v>71</v>
+      <c r="B39">
+        <v>1105</v>
       </c>
       <c r="C39" t="s">
         <v>74</v>
@@ -3839,8 +3839,8 @@
       <c r="D39" t="s">
         <v>80</v>
       </c>
-      <c r="E39" t="s">
-        <v>83</v>
+      <c r="E39">
+        <v>2023</v>
       </c>
       <c r="F39" t="s">
         <v>84</v>
@@ -3889,8 +3889,8 @@
       <c r="A40" t="s">
         <v>64</v>
       </c>
-      <c r="B40" t="s">
-        <v>72</v>
+      <c r="B40">
+        <v>1143</v>
       </c>
       <c r="C40" t="s">
         <v>75</v>
@@ -3898,8 +3898,8 @@
       <c r="D40" t="s">
         <v>81</v>
       </c>
-      <c r="E40" t="s">
-        <v>83</v>
+      <c r="E40">
+        <v>2023</v>
       </c>
       <c r="F40" t="s">
         <v>84</v>
@@ -3987,8 +3987,8 @@
       <c r="A41" t="s">
         <v>65</v>
       </c>
-      <c r="B41" t="s">
-        <v>73</v>
+      <c r="B41">
+        <v>1321</v>
       </c>
       <c r="C41" t="s">
         <v>75</v>
@@ -3996,8 +3996,8 @@
       <c r="D41" t="s">
         <v>82</v>
       </c>
-      <c r="E41" t="s">
-        <v>83</v>
+      <c r="E41">
+        <v>2023</v>
       </c>
       <c r="F41" t="s">
         <v>84</v>
@@ -4060,6 +4060,1304 @@
         <v>45181.72148148148</v>
       </c>
       <c r="BF41" s="2">
+        <v>45184.58322916667</v>
+      </c>
+    </row>
+    <row r="42" spans="1:58">
+      <c r="A42" t="s">
+        <v>58</v>
+      </c>
+      <c r="B42">
+        <v>48</v>
+      </c>
+      <c r="C42" t="s">
+        <v>74</v>
+      </c>
+      <c r="D42" t="s">
+        <v>76</v>
+      </c>
+      <c r="E42">
+        <v>2023</v>
+      </c>
+      <c r="F42" t="s">
+        <v>84</v>
+      </c>
+      <c r="G42" t="s">
+        <v>85</v>
+      </c>
+      <c r="H42" t="b">
+        <v>1</v>
+      </c>
+      <c r="I42" s="2">
+        <v>45179.39792824074</v>
+      </c>
+      <c r="J42" s="2">
+        <v>45179.50267361111</v>
+      </c>
+      <c r="K42" s="2">
+        <v>45179.52646990741</v>
+      </c>
+      <c r="L42" s="2">
+        <v>45179.59795138889</v>
+      </c>
+      <c r="M42" s="2">
+        <v>45179.72765046296</v>
+      </c>
+      <c r="N42" s="2">
+        <v>45179.75509259259</v>
+      </c>
+      <c r="O42" s="2">
+        <v>45179.76221064815</v>
+      </c>
+      <c r="P42" s="2">
+        <v>45179.81621527778</v>
+      </c>
+      <c r="Q42" s="2">
+        <v>45179.87998842593</v>
+      </c>
+      <c r="R42" s="2">
+        <v>45180.00331018519</v>
+      </c>
+      <c r="S42" s="2">
+        <v>45180.16604166666</v>
+      </c>
+      <c r="T42" s="2">
+        <v>45180.21908564815</v>
+      </c>
+      <c r="U42" s="2">
+        <v>45180.23003472222</v>
+      </c>
+      <c r="V42" s="2">
+        <v>45180.27650462963</v>
+      </c>
+      <c r="W42" s="2">
+        <v>45180.42538194444</v>
+      </c>
+      <c r="X42" s="2">
+        <v>45180.468125</v>
+      </c>
+      <c r="Z42" s="2">
+        <v>45180.58392361111</v>
+      </c>
+      <c r="BF42" s="2">
+        <v>45182.23497685185</v>
+      </c>
+    </row>
+    <row r="43" spans="1:58">
+      <c r="A43" t="s">
+        <v>59</v>
+      </c>
+      <c r="B43">
+        <v>275</v>
+      </c>
+      <c r="C43" t="s">
+        <v>74</v>
+      </c>
+      <c r="D43" t="s">
+        <v>77</v>
+      </c>
+      <c r="E43">
+        <v>2023</v>
+      </c>
+      <c r="F43" t="s">
+        <v>84</v>
+      </c>
+      <c r="G43" t="s">
+        <v>85</v>
+      </c>
+      <c r="H43" t="b">
+        <v>1</v>
+      </c>
+      <c r="I43" s="2">
+        <v>45179.38922453704</v>
+      </c>
+      <c r="J43" s="2">
+        <v>45179.54383101852</v>
+      </c>
+      <c r="K43" s="2">
+        <v>45179.58179398148</v>
+      </c>
+      <c r="L43" s="2">
+        <v>45179.70383101852</v>
+      </c>
+      <c r="M43" s="2">
+        <v>45179.94988425926</v>
+      </c>
+      <c r="N43" s="2">
+        <v>45179.99344907407</v>
+      </c>
+      <c r="O43" s="2">
+        <v>45179.9962037037</v>
+      </c>
+      <c r="P43" s="2">
+        <v>45180.10306712963</v>
+      </c>
+      <c r="Q43" s="2">
+        <v>45180.2472337963</v>
+      </c>
+      <c r="R43" s="2">
+        <v>45180.53554398148</v>
+      </c>
+      <c r="S43" s="2">
+        <v>45180.90009259259</v>
+      </c>
+      <c r="T43" s="2">
+        <v>45181.00655092593</v>
+      </c>
+      <c r="U43" s="2">
+        <v>45181.20306712963</v>
+      </c>
+      <c r="V43" s="2">
+        <v>45181.27269675926</v>
+      </c>
+      <c r="W43" s="2">
+        <v>45181.55180555556</v>
+      </c>
+      <c r="X43" s="2">
+        <v>45181.63777777777</v>
+      </c>
+      <c r="Y43" s="2">
+        <v>45181.7540162037</v>
+      </c>
+      <c r="Z43" s="2">
+        <v>45181.89640046296</v>
+      </c>
+      <c r="AA43" s="2">
+        <v>45181.98230324074</v>
+      </c>
+      <c r="AB43" s="2">
+        <v>45182.08106481482</v>
+      </c>
+      <c r="AC43" s="2">
+        <v>45182.35355324074</v>
+      </c>
+      <c r="AD43" s="2">
+        <v>45182.45358796296</v>
+      </c>
+      <c r="AE43" s="2">
+        <v>45182.59913194444</v>
+      </c>
+      <c r="AF43" s="2">
+        <v>45182.72322916667</v>
+      </c>
+      <c r="AG43" s="2">
+        <v>45182.83815972223</v>
+      </c>
+      <c r="AK43" s="2">
+        <v>45183.06462962963</v>
+      </c>
+      <c r="BF43" s="2">
+        <v>45185.59189814814</v>
+      </c>
+    </row>
+    <row r="44" spans="1:58">
+      <c r="A44" t="s">
+        <v>60</v>
+      </c>
+      <c r="B44">
+        <v>493</v>
+      </c>
+      <c r="C44" t="s">
+        <v>75</v>
+      </c>
+      <c r="D44" t="s">
+        <v>78</v>
+      </c>
+      <c r="E44">
+        <v>2023</v>
+      </c>
+      <c r="F44" t="s">
+        <v>84</v>
+      </c>
+      <c r="G44" t="s">
+        <v>85</v>
+      </c>
+      <c r="H44" t="b">
+        <v>1</v>
+      </c>
+      <c r="I44" s="2">
+        <v>45179.409375</v>
+      </c>
+      <c r="J44" s="2">
+        <v>45179.55034722222</v>
+      </c>
+      <c r="K44" s="2">
+        <v>45179.59763888889</v>
+      </c>
+      <c r="L44" s="2">
+        <v>45179.72980324074</v>
+      </c>
+      <c r="M44" s="2">
+        <v>45179.96844907408</v>
+      </c>
+      <c r="N44" s="2">
+        <v>45180.01599537037</v>
+      </c>
+      <c r="O44" s="2">
+        <v>45180.11148148148</v>
+      </c>
+      <c r="P44" s="2">
+        <v>45180.24331018519</v>
+      </c>
+      <c r="Q44" s="2">
+        <v>45180.3828587963</v>
+      </c>
+      <c r="R44" s="2">
+        <v>45180.71607638889</v>
+      </c>
+      <c r="S44" s="2">
+        <v>45180.96011574074</v>
+      </c>
+      <c r="T44" s="2">
+        <v>45181.15980324074</v>
+      </c>
+      <c r="U44" s="2">
+        <v>45181.24869212963</v>
+      </c>
+      <c r="V44" s="2">
+        <v>45181.34960648148</v>
+      </c>
+      <c r="W44" s="2">
+        <v>45181.65403935185</v>
+      </c>
+      <c r="X44" s="2">
+        <v>45181.75313657407</v>
+      </c>
+      <c r="Y44" s="2">
+        <v>45181.81587962963</v>
+      </c>
+      <c r="Z44" s="2">
+        <v>45181.9002662037</v>
+      </c>
+      <c r="AA44" s="2">
+        <v>45181.90072916666</v>
+      </c>
+      <c r="AB44" s="2">
+        <v>45182.20228009259</v>
+      </c>
+      <c r="AC44" s="2">
+        <v>45182.37464120371</v>
+      </c>
+      <c r="AD44" s="2">
+        <v>45182.49806712963</v>
+      </c>
+      <c r="AE44" s="2">
+        <v>45182.64914351852</v>
+      </c>
+      <c r="BF44" s="2">
+        <v>45183.00606481481</v>
+      </c>
+    </row>
+    <row r="45" spans="1:58">
+      <c r="A45" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45">
+        <v>540</v>
+      </c>
+      <c r="C45" t="s">
+        <v>75</v>
+      </c>
+      <c r="D45" t="s">
+        <v>77</v>
+      </c>
+      <c r="E45">
+        <v>2023</v>
+      </c>
+      <c r="F45" t="s">
+        <v>84</v>
+      </c>
+      <c r="G45" t="s">
+        <v>86</v>
+      </c>
+      <c r="H45" t="b">
+        <v>1</v>
+      </c>
+      <c r="I45" s="2">
+        <v>45179.39790509259</v>
+      </c>
+      <c r="J45" s="2">
+        <v>45179.53548611111</v>
+      </c>
+      <c r="K45" s="2">
+        <v>45179.57420138889</v>
+      </c>
+      <c r="L45" s="2">
+        <v>45179.70348379629</v>
+      </c>
+      <c r="M45" s="2">
+        <v>45179.93878472222</v>
+      </c>
+      <c r="N45" s="2">
+        <v>45179.99392361111</v>
+      </c>
+      <c r="O45" s="2">
+        <v>45180.06231481482</v>
+      </c>
+      <c r="BF45" s="2">
+        <v>45182.84180555555</v>
+      </c>
+    </row>
+    <row r="46" spans="1:58">
+      <c r="A46" t="s">
+        <v>62</v>
+      </c>
+      <c r="B46">
+        <v>665</v>
+      </c>
+      <c r="C46" t="s">
+        <v>74</v>
+      </c>
+      <c r="D46" t="s">
+        <v>79</v>
+      </c>
+      <c r="E46">
+        <v>2023</v>
+      </c>
+      <c r="F46" t="s">
+        <v>84</v>
+      </c>
+      <c r="G46" t="s">
+        <v>86</v>
+      </c>
+      <c r="H46" t="b">
+        <v>1</v>
+      </c>
+      <c r="I46" s="2">
+        <v>45179.39430555556</v>
+      </c>
+      <c r="J46" s="2">
+        <v>45179.50248842593</v>
+      </c>
+      <c r="K46" s="2">
+        <v>45179.528125</v>
+      </c>
+      <c r="L46" s="2">
+        <v>45179.60185185185</v>
+      </c>
+      <c r="M46" s="2">
+        <v>45179.73332175926</v>
+      </c>
+      <c r="N46" s="2">
+        <v>45179.76197916667</v>
+      </c>
+      <c r="O46" s="2">
+        <v>45179.7722337963</v>
+      </c>
+      <c r="P46" s="2">
+        <v>45179.82659722222</v>
+      </c>
+      <c r="Q46" s="2">
+        <v>45179.88775462963</v>
+      </c>
+      <c r="R46" s="2">
+        <v>45180.0141087963</v>
+      </c>
+      <c r="S46" s="2">
+        <v>45180.17658564815</v>
+      </c>
+      <c r="T46" s="2">
+        <v>45180.2478125</v>
+      </c>
+      <c r="V46" s="2">
+        <v>45180.32322916666</v>
+      </c>
+      <c r="W46" s="2">
+        <v>45180.49724537037</v>
+      </c>
+      <c r="X46" s="2">
+        <v>45180.54726851852</v>
+      </c>
+      <c r="Z46" s="2">
+        <v>45180.58400462963</v>
+      </c>
+      <c r="BF46" s="2">
+        <v>45184.37396990741</v>
+      </c>
+    </row>
+    <row r="47" spans="1:58">
+      <c r="A47" t="s">
+        <v>63</v>
+      </c>
+      <c r="B47">
+        <v>1105</v>
+      </c>
+      <c r="C47" t="s">
+        <v>74</v>
+      </c>
+      <c r="D47" t="s">
+        <v>80</v>
+      </c>
+      <c r="E47">
+        <v>2023</v>
+      </c>
+      <c r="F47" t="s">
+        <v>84</v>
+      </c>
+      <c r="G47" t="s">
+        <v>86</v>
+      </c>
+      <c r="H47" t="b">
+        <v>1</v>
+      </c>
+      <c r="I47" s="2">
+        <v>45179.49493055556</v>
+      </c>
+      <c r="J47" s="2">
+        <v>45179.64465277778</v>
+      </c>
+      <c r="K47" s="2">
+        <v>45179.68689814815</v>
+      </c>
+      <c r="L47" s="2">
+        <v>45179.81511574074</v>
+      </c>
+      <c r="M47" s="2">
+        <v>45180.12268518518</v>
+      </c>
+      <c r="N47" s="2">
+        <v>45180.19484953704</v>
+      </c>
+      <c r="O47" s="2">
+        <v>45180.25997685185</v>
+      </c>
+      <c r="Q47" s="2">
+        <v>45180.52630787037</v>
+      </c>
+      <c r="R47" s="2">
+        <v>45180.82422453703</v>
+      </c>
+      <c r="S47" s="2">
+        <v>45181.24221064815</v>
+      </c>
+      <c r="BF47" s="2">
+        <v>45183.73302083334</v>
+      </c>
+    </row>
+    <row r="48" spans="1:58">
+      <c r="A48" t="s">
+        <v>64</v>
+      </c>
+      <c r="B48">
+        <v>1143</v>
+      </c>
+      <c r="C48" t="s">
+        <v>75</v>
+      </c>
+      <c r="D48" t="s">
+        <v>81</v>
+      </c>
+      <c r="E48">
+        <v>2023</v>
+      </c>
+      <c r="F48" t="s">
+        <v>84</v>
+      </c>
+      <c r="G48" t="s">
+        <v>87</v>
+      </c>
+      <c r="H48" t="b">
+        <v>1</v>
+      </c>
+      <c r="I48" s="2">
+        <v>45179.48607638889</v>
+      </c>
+      <c r="J48" s="2">
+        <v>45179.64658564814</v>
+      </c>
+      <c r="K48" s="2">
+        <v>45179.7028587963</v>
+      </c>
+      <c r="L48" s="2">
+        <v>45179.83604166667</v>
+      </c>
+      <c r="M48" s="2">
+        <v>45180.12891203703</v>
+      </c>
+      <c r="N48" s="2">
+        <v>45180.18069444445</v>
+      </c>
+      <c r="O48" s="2">
+        <v>45180.28619212963</v>
+      </c>
+      <c r="Q48" s="2">
+        <v>45180.49460648148</v>
+      </c>
+      <c r="R48" s="2">
+        <v>45180.77678240741</v>
+      </c>
+      <c r="S48" s="2">
+        <v>45181.10384259259</v>
+      </c>
+      <c r="T48" s="2">
+        <v>45181.21434027778</v>
+      </c>
+      <c r="U48" s="2">
+        <v>45181.30199074074</v>
+      </c>
+      <c r="V48" s="2">
+        <v>45181.37020833333</v>
+      </c>
+      <c r="W48" s="2">
+        <v>45181.58256944444</v>
+      </c>
+      <c r="X48" s="2">
+        <v>45181.65321759259</v>
+      </c>
+      <c r="Y48" s="2">
+        <v>45181.74200231482</v>
+      </c>
+      <c r="Z48" s="2">
+        <v>45181.88</v>
+      </c>
+      <c r="AA48" s="2">
+        <v>45181.96909722222</v>
+      </c>
+      <c r="AB48" s="2">
+        <v>45182.0671412037</v>
+      </c>
+      <c r="AD48" s="2">
+        <v>45182.3734375</v>
+      </c>
+      <c r="AE48" s="2">
+        <v>45182.5744675926</v>
+      </c>
+      <c r="AF48" s="2">
+        <v>45182.66641203704</v>
+      </c>
+      <c r="AG48" s="2">
+        <v>45182.74886574074</v>
+      </c>
+      <c r="BF48" s="2">
+        <v>45185.71348379629</v>
+      </c>
+    </row>
+    <row r="49" spans="1:58">
+      <c r="A49" t="s">
+        <v>65</v>
+      </c>
+      <c r="B49">
+        <v>1321</v>
+      </c>
+      <c r="C49" t="s">
+        <v>75</v>
+      </c>
+      <c r="D49" t="s">
+        <v>82</v>
+      </c>
+      <c r="E49">
+        <v>2023</v>
+      </c>
+      <c r="F49" t="s">
+        <v>84</v>
+      </c>
+      <c r="G49" t="s">
+        <v>87</v>
+      </c>
+      <c r="H49" t="b">
+        <v>1</v>
+      </c>
+      <c r="I49" s="2">
+        <v>45179.47435185185</v>
+      </c>
+      <c r="J49" s="2">
+        <v>45179.63296296296</v>
+      </c>
+      <c r="K49" s="2">
+        <v>45179.68140046296</v>
+      </c>
+      <c r="L49" s="2">
+        <v>45179.80612268519</v>
+      </c>
+      <c r="M49" s="2">
+        <v>45180.06925925926</v>
+      </c>
+      <c r="N49" s="2">
+        <v>45180.1246875</v>
+      </c>
+      <c r="O49" s="2">
+        <v>45180.17931712963</v>
+      </c>
+      <c r="P49" s="2">
+        <v>45180.28188657408</v>
+      </c>
+      <c r="Q49" s="2">
+        <v>45180.41796296297</v>
+      </c>
+      <c r="R49" s="2">
+        <v>45180.68553240741</v>
+      </c>
+      <c r="S49" s="2">
+        <v>45180.97909722223</v>
+      </c>
+      <c r="T49" s="2">
+        <v>45181.17892361111</v>
+      </c>
+      <c r="U49" s="2">
+        <v>45181.2145949074</v>
+      </c>
+      <c r="V49" s="2">
+        <v>45181.29107638889</v>
+      </c>
+      <c r="W49" s="2">
+        <v>45181.51983796297</v>
+      </c>
+      <c r="X49" s="2">
+        <v>45181.60017361111</v>
+      </c>
+      <c r="AA49" s="2">
+        <v>45181.72148148148</v>
+      </c>
+      <c r="BF49" s="2">
+        <v>45184.58322916667</v>
+      </c>
+    </row>
+    <row r="50" spans="1:58">
+      <c r="A50" t="s">
+        <v>58</v>
+      </c>
+      <c r="B50" t="s">
+        <v>66</v>
+      </c>
+      <c r="C50" t="s">
+        <v>74</v>
+      </c>
+      <c r="D50" t="s">
+        <v>76</v>
+      </c>
+      <c r="E50" t="s">
+        <v>83</v>
+      </c>
+      <c r="F50" t="s">
+        <v>84</v>
+      </c>
+      <c r="G50" t="s">
+        <v>85</v>
+      </c>
+      <c r="H50" t="b">
+        <v>1</v>
+      </c>
+      <c r="I50" s="2">
+        <v>45179.39792824074</v>
+      </c>
+      <c r="J50" s="2">
+        <v>45179.50267361111</v>
+      </c>
+      <c r="K50" s="2">
+        <v>45179.52646990741</v>
+      </c>
+      <c r="L50" s="2">
+        <v>45179.59795138889</v>
+      </c>
+      <c r="M50" s="2">
+        <v>45179.72765046296</v>
+      </c>
+      <c r="N50" s="2">
+        <v>45179.75509259259</v>
+      </c>
+      <c r="O50" s="2">
+        <v>45179.76221064815</v>
+      </c>
+      <c r="P50" s="2">
+        <v>45179.81621527778</v>
+      </c>
+      <c r="Q50" s="2">
+        <v>45179.87998842593</v>
+      </c>
+      <c r="R50" s="2">
+        <v>45180.00331018519</v>
+      </c>
+      <c r="S50" s="2">
+        <v>45180.16604166666</v>
+      </c>
+      <c r="T50" s="2">
+        <v>45180.21908564815</v>
+      </c>
+      <c r="U50" s="2">
+        <v>45180.23003472222</v>
+      </c>
+      <c r="V50" s="2">
+        <v>45180.27650462963</v>
+      </c>
+      <c r="W50" s="2">
+        <v>45180.42538194444</v>
+      </c>
+      <c r="X50" s="2">
+        <v>45180.468125</v>
+      </c>
+      <c r="Z50" s="2">
+        <v>45180.58392361111</v>
+      </c>
+      <c r="BF50" s="2">
+        <v>45182.23497685185</v>
+      </c>
+    </row>
+    <row r="51" spans="1:58">
+      <c r="A51" t="s">
+        <v>59</v>
+      </c>
+      <c r="B51" t="s">
+        <v>67</v>
+      </c>
+      <c r="C51" t="s">
+        <v>74</v>
+      </c>
+      <c r="D51" t="s">
+        <v>77</v>
+      </c>
+      <c r="E51" t="s">
+        <v>83</v>
+      </c>
+      <c r="F51" t="s">
+        <v>84</v>
+      </c>
+      <c r="G51" t="s">
+        <v>85</v>
+      </c>
+      <c r="H51" t="b">
+        <v>1</v>
+      </c>
+      <c r="I51" s="2">
+        <v>45179.38922453704</v>
+      </c>
+      <c r="J51" s="2">
+        <v>45179.54383101852</v>
+      </c>
+      <c r="K51" s="2">
+        <v>45179.58179398148</v>
+      </c>
+      <c r="L51" s="2">
+        <v>45179.70383101852</v>
+      </c>
+      <c r="M51" s="2">
+        <v>45179.94988425926</v>
+      </c>
+      <c r="N51" s="2">
+        <v>45179.99344907407</v>
+      </c>
+      <c r="O51" s="2">
+        <v>45179.9962037037</v>
+      </c>
+      <c r="P51" s="2">
+        <v>45180.10306712963</v>
+      </c>
+      <c r="Q51" s="2">
+        <v>45180.2472337963</v>
+      </c>
+      <c r="R51" s="2">
+        <v>45180.53554398148</v>
+      </c>
+      <c r="S51" s="2">
+        <v>45180.90009259259</v>
+      </c>
+      <c r="T51" s="2">
+        <v>45181.00655092593</v>
+      </c>
+      <c r="U51" s="2">
+        <v>45181.20306712963</v>
+      </c>
+      <c r="V51" s="2">
+        <v>45181.27269675926</v>
+      </c>
+      <c r="W51" s="2">
+        <v>45181.55180555556</v>
+      </c>
+      <c r="X51" s="2">
+        <v>45181.63777777777</v>
+      </c>
+      <c r="Y51" s="2">
+        <v>45181.7540162037</v>
+      </c>
+      <c r="Z51" s="2">
+        <v>45181.89640046296</v>
+      </c>
+      <c r="AA51" s="2">
+        <v>45181.98230324074</v>
+      </c>
+      <c r="AB51" s="2">
+        <v>45182.08106481482</v>
+      </c>
+      <c r="AC51" s="2">
+        <v>45182.35355324074</v>
+      </c>
+      <c r="AD51" s="2">
+        <v>45182.45358796296</v>
+      </c>
+      <c r="AE51" s="2">
+        <v>45182.59913194444</v>
+      </c>
+      <c r="AF51" s="2">
+        <v>45182.72322916667</v>
+      </c>
+      <c r="AG51" s="2">
+        <v>45182.83815972223</v>
+      </c>
+      <c r="AK51" s="2">
+        <v>45183.06462962963</v>
+      </c>
+      <c r="BF51" s="2">
+        <v>45185.59189814814</v>
+      </c>
+    </row>
+    <row r="52" spans="1:58">
+      <c r="A52" t="s">
+        <v>60</v>
+      </c>
+      <c r="B52" t="s">
+        <v>68</v>
+      </c>
+      <c r="C52" t="s">
+        <v>75</v>
+      </c>
+      <c r="D52" t="s">
+        <v>78</v>
+      </c>
+      <c r="E52" t="s">
+        <v>83</v>
+      </c>
+      <c r="F52" t="s">
+        <v>84</v>
+      </c>
+      <c r="G52" t="s">
+        <v>85</v>
+      </c>
+      <c r="H52" t="b">
+        <v>1</v>
+      </c>
+      <c r="I52" s="2">
+        <v>45179.409375</v>
+      </c>
+      <c r="J52" s="2">
+        <v>45179.55034722222</v>
+      </c>
+      <c r="K52" s="2">
+        <v>45179.59763888889</v>
+      </c>
+      <c r="L52" s="2">
+        <v>45179.72980324074</v>
+      </c>
+      <c r="M52" s="2">
+        <v>45179.96844907408</v>
+      </c>
+      <c r="N52" s="2">
+        <v>45180.01599537037</v>
+      </c>
+      <c r="O52" s="2">
+        <v>45180.11148148148</v>
+      </c>
+      <c r="P52" s="2">
+        <v>45180.24331018519</v>
+      </c>
+      <c r="Q52" s="2">
+        <v>45180.3828587963</v>
+      </c>
+      <c r="R52" s="2">
+        <v>45180.71607638889</v>
+      </c>
+      <c r="S52" s="2">
+        <v>45180.96011574074</v>
+      </c>
+      <c r="T52" s="2">
+        <v>45181.15980324074</v>
+      </c>
+      <c r="U52" s="2">
+        <v>45181.24869212963</v>
+      </c>
+      <c r="V52" s="2">
+        <v>45181.34960648148</v>
+      </c>
+      <c r="W52" s="2">
+        <v>45181.65403935185</v>
+      </c>
+      <c r="X52" s="2">
+        <v>45181.75313657407</v>
+      </c>
+      <c r="Y52" s="2">
+        <v>45181.81587962963</v>
+      </c>
+      <c r="Z52" s="2">
+        <v>45181.9002662037</v>
+      </c>
+      <c r="AA52" s="2">
+        <v>45181.90072916666</v>
+      </c>
+      <c r="AB52" s="2">
+        <v>45182.20228009259</v>
+      </c>
+      <c r="AC52" s="2">
+        <v>45182.37464120371</v>
+      </c>
+      <c r="AD52" s="2">
+        <v>45182.49806712963</v>
+      </c>
+      <c r="AE52" s="2">
+        <v>45182.64914351852</v>
+      </c>
+      <c r="BF52" s="2">
+        <v>45183.00606481481</v>
+      </c>
+    </row>
+    <row r="53" spans="1:58">
+      <c r="A53" t="s">
+        <v>61</v>
+      </c>
+      <c r="B53" t="s">
+        <v>69</v>
+      </c>
+      <c r="C53" t="s">
+        <v>75</v>
+      </c>
+      <c r="D53" t="s">
+        <v>77</v>
+      </c>
+      <c r="E53" t="s">
+        <v>83</v>
+      </c>
+      <c r="F53" t="s">
+        <v>84</v>
+      </c>
+      <c r="G53" t="s">
+        <v>86</v>
+      </c>
+      <c r="H53" t="b">
+        <v>1</v>
+      </c>
+      <c r="I53" s="2">
+        <v>45179.39790509259</v>
+      </c>
+      <c r="J53" s="2">
+        <v>45179.53548611111</v>
+      </c>
+      <c r="K53" s="2">
+        <v>45179.57420138889</v>
+      </c>
+      <c r="L53" s="2">
+        <v>45179.70348379629</v>
+      </c>
+      <c r="M53" s="2">
+        <v>45179.93878472222</v>
+      </c>
+      <c r="N53" s="2">
+        <v>45179.99392361111</v>
+      </c>
+      <c r="O53" s="2">
+        <v>45180.06231481482</v>
+      </c>
+      <c r="BF53" s="2">
+        <v>45182.84180555555</v>
+      </c>
+    </row>
+    <row r="54" spans="1:58">
+      <c r="A54" t="s">
+        <v>62</v>
+      </c>
+      <c r="B54" t="s">
+        <v>70</v>
+      </c>
+      <c r="C54" t="s">
+        <v>74</v>
+      </c>
+      <c r="D54" t="s">
+        <v>79</v>
+      </c>
+      <c r="E54" t="s">
+        <v>83</v>
+      </c>
+      <c r="F54" t="s">
+        <v>84</v>
+      </c>
+      <c r="G54" t="s">
+        <v>86</v>
+      </c>
+      <c r="H54" t="b">
+        <v>1</v>
+      </c>
+      <c r="I54" s="2">
+        <v>45179.39430555556</v>
+      </c>
+      <c r="J54" s="2">
+        <v>45179.50248842593</v>
+      </c>
+      <c r="K54" s="2">
+        <v>45179.528125</v>
+      </c>
+      <c r="L54" s="2">
+        <v>45179.60185185185</v>
+      </c>
+      <c r="M54" s="2">
+        <v>45179.73332175926</v>
+      </c>
+      <c r="N54" s="2">
+        <v>45179.76197916667</v>
+      </c>
+      <c r="O54" s="2">
+        <v>45179.7722337963</v>
+      </c>
+      <c r="P54" s="2">
+        <v>45179.82659722222</v>
+      </c>
+      <c r="Q54" s="2">
+        <v>45179.88775462963</v>
+      </c>
+      <c r="R54" s="2">
+        <v>45180.0141087963</v>
+      </c>
+      <c r="S54" s="2">
+        <v>45180.17658564815</v>
+      </c>
+      <c r="T54" s="2">
+        <v>45180.2478125</v>
+      </c>
+      <c r="V54" s="2">
+        <v>45180.32322916666</v>
+      </c>
+      <c r="W54" s="2">
+        <v>45180.49724537037</v>
+      </c>
+      <c r="X54" s="2">
+        <v>45180.54726851852</v>
+      </c>
+      <c r="Z54" s="2">
+        <v>45180.58400462963</v>
+      </c>
+      <c r="BF54" s="2">
+        <v>45184.37396990741</v>
+      </c>
+    </row>
+    <row r="55" spans="1:58">
+      <c r="A55" t="s">
+        <v>63</v>
+      </c>
+      <c r="B55" t="s">
+        <v>71</v>
+      </c>
+      <c r="C55" t="s">
+        <v>74</v>
+      </c>
+      <c r="D55" t="s">
+        <v>80</v>
+      </c>
+      <c r="E55" t="s">
+        <v>83</v>
+      </c>
+      <c r="F55" t="s">
+        <v>84</v>
+      </c>
+      <c r="G55" t="s">
+        <v>86</v>
+      </c>
+      <c r="H55" t="b">
+        <v>1</v>
+      </c>
+      <c r="I55" s="2">
+        <v>45179.49493055556</v>
+      </c>
+      <c r="J55" s="2">
+        <v>45179.64465277778</v>
+      </c>
+      <c r="K55" s="2">
+        <v>45179.68689814815</v>
+      </c>
+      <c r="L55" s="2">
+        <v>45179.81511574074</v>
+      </c>
+      <c r="M55" s="2">
+        <v>45180.12268518518</v>
+      </c>
+      <c r="N55" s="2">
+        <v>45180.19484953704</v>
+      </c>
+      <c r="O55" s="2">
+        <v>45180.25997685185</v>
+      </c>
+      <c r="Q55" s="2">
+        <v>45180.52630787037</v>
+      </c>
+      <c r="R55" s="2">
+        <v>45180.82422453703</v>
+      </c>
+      <c r="S55" s="2">
+        <v>45181.24221064815</v>
+      </c>
+      <c r="BF55" s="2">
+        <v>45183.73302083334</v>
+      </c>
+    </row>
+    <row r="56" spans="1:58">
+      <c r="A56" t="s">
+        <v>64</v>
+      </c>
+      <c r="B56" t="s">
+        <v>72</v>
+      </c>
+      <c r="C56" t="s">
+        <v>75</v>
+      </c>
+      <c r="D56" t="s">
+        <v>81</v>
+      </c>
+      <c r="E56" t="s">
+        <v>83</v>
+      </c>
+      <c r="F56" t="s">
+        <v>84</v>
+      </c>
+      <c r="G56" t="s">
+        <v>87</v>
+      </c>
+      <c r="H56" t="b">
+        <v>1</v>
+      </c>
+      <c r="I56" s="2">
+        <v>45179.48607638889</v>
+      </c>
+      <c r="J56" s="2">
+        <v>45179.64658564814</v>
+      </c>
+      <c r="K56" s="2">
+        <v>45179.7028587963</v>
+      </c>
+      <c r="L56" s="2">
+        <v>45179.83604166667</v>
+      </c>
+      <c r="M56" s="2">
+        <v>45180.12891203703</v>
+      </c>
+      <c r="N56" s="2">
+        <v>45180.18069444445</v>
+      </c>
+      <c r="O56" s="2">
+        <v>45180.28619212963</v>
+      </c>
+      <c r="Q56" s="2">
+        <v>45180.49460648148</v>
+      </c>
+      <c r="R56" s="2">
+        <v>45180.77678240741</v>
+      </c>
+      <c r="S56" s="2">
+        <v>45181.10384259259</v>
+      </c>
+      <c r="T56" s="2">
+        <v>45181.21434027778</v>
+      </c>
+      <c r="U56" s="2">
+        <v>45181.30199074074</v>
+      </c>
+      <c r="V56" s="2">
+        <v>45181.37020833333</v>
+      </c>
+      <c r="W56" s="2">
+        <v>45181.58256944444</v>
+      </c>
+      <c r="X56" s="2">
+        <v>45181.65321759259</v>
+      </c>
+      <c r="Y56" s="2">
+        <v>45181.74200231482</v>
+      </c>
+      <c r="Z56" s="2">
+        <v>45181.88</v>
+      </c>
+      <c r="AA56" s="2">
+        <v>45181.96909722222</v>
+      </c>
+      <c r="AB56" s="2">
+        <v>45182.0671412037</v>
+      </c>
+      <c r="AD56" s="2">
+        <v>45182.3734375</v>
+      </c>
+      <c r="AE56" s="2">
+        <v>45182.5744675926</v>
+      </c>
+      <c r="AF56" s="2">
+        <v>45182.66641203704</v>
+      </c>
+      <c r="AG56" s="2">
+        <v>45182.74886574074</v>
+      </c>
+      <c r="BF56" s="2">
+        <v>45185.71348379629</v>
+      </c>
+    </row>
+    <row r="57" spans="1:58">
+      <c r="A57" t="s">
+        <v>65</v>
+      </c>
+      <c r="B57" t="s">
+        <v>73</v>
+      </c>
+      <c r="C57" t="s">
+        <v>75</v>
+      </c>
+      <c r="D57" t="s">
+        <v>82</v>
+      </c>
+      <c r="E57" t="s">
+        <v>83</v>
+      </c>
+      <c r="F57" t="s">
+        <v>84</v>
+      </c>
+      <c r="G57" t="s">
+        <v>87</v>
+      </c>
+      <c r="H57" t="b">
+        <v>1</v>
+      </c>
+      <c r="I57" s="2">
+        <v>45179.47435185185</v>
+      </c>
+      <c r="J57" s="2">
+        <v>45179.63296296296</v>
+      </c>
+      <c r="K57" s="2">
+        <v>45179.68140046296</v>
+      </c>
+      <c r="L57" s="2">
+        <v>45179.80612268519</v>
+      </c>
+      <c r="M57" s="2">
+        <v>45180.06925925926</v>
+      </c>
+      <c r="N57" s="2">
+        <v>45180.1246875</v>
+      </c>
+      <c r="O57" s="2">
+        <v>45180.17931712963</v>
+      </c>
+      <c r="P57" s="2">
+        <v>45180.28188657408</v>
+      </c>
+      <c r="Q57" s="2">
+        <v>45180.41796296297</v>
+      </c>
+      <c r="R57" s="2">
+        <v>45180.68553240741</v>
+      </c>
+      <c r="S57" s="2">
+        <v>45180.97909722223</v>
+      </c>
+      <c r="T57" s="2">
+        <v>45181.17892361111</v>
+      </c>
+      <c r="U57" s="2">
+        <v>45181.2145949074</v>
+      </c>
+      <c r="V57" s="2">
+        <v>45181.29107638889</v>
+      </c>
+      <c r="W57" s="2">
+        <v>45181.51983796297</v>
+      </c>
+      <c r="X57" s="2">
+        <v>45181.60017361111</v>
+      </c>
+      <c r="AA57" s="2">
+        <v>45181.72148148148</v>
+      </c>
+      <c r="BF57" s="2">
         <v>45184.58322916667</v>
       </c>
     </row>
